--- a/basedatos_partidas/salida/descompuestos/09.16.02.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/09.16.02.010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,44 +534,44 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-CONS-DEM</t>
+          <t>MQ-TALADRO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Consumibles de demolición: puntas y cinceles de martillo, discos de corte y hojas de espátula.</t>
+          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.66</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="11">
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>Subtotal materiales:</t>
+          <t>Subtotal equipo y maquinaria:</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.66</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -580,14 +580,14 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>Equipo y maquinaria</t>
+          <t>Mano de obra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MQ-TALADRO</t>
+          <t>MO-OF1-MON</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -597,146 +597,100 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
+          <t>Oficial de 1ª montador de prefabricados interiores.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2.25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal equipo y maquinaria:</t>
-        </is>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MO-AYU</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ayudante.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.25</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal mano de obra:</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>Mano de obra</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MO-OF1-MON</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Oficial de 1ª montador de prefabricados interiores.</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>55</v>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MO-AYU</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Ayudante.</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>74.75</v>
       </c>
       <c r="H17" t="n">
-        <v>17.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal mano de obra:</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>75.41</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Costes directos (1+2+3+4):</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n">
-        <v>76.16</v>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Costes directos (1+2+3):</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="5" t="n">
+        <v>75.5</v>
       </c>
     </row>
   </sheetData>
